--- a/research/AGL.NZ/Reports/AGL.NZ_DCF_Model.xlsx
+++ b/research/AGL.NZ/Reports/AGL.NZ_DCF_Model.xlsx
@@ -2762,9 +2762,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B9" s="7">
         <v>10.9</v>
